--- a/active_skills_spec_12.xlsx
+++ b/active_skills_spec_12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SI1399\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\FirstGameApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1146BB-C02B-4BEF-8C1E-8E541551B5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1941C8FC-73C0-493D-A027-621ABDEA4E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" r:id="rId1"/>
@@ -183,9 +183,6 @@
     <t>arc_bolt</t>
   </si>
   <si>
-    <t>奧術飛矢</t>
-  </si>
-  <si>
     <t>auto</t>
   </si>
   <si>
@@ -219,9 +216,6 @@
     <t>single_target, homing, arcane, starter</t>
   </si>
   <si>
-    <t>聖環飛刃</t>
-  </si>
-  <si>
     <t>orbit</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>orbit, melee, sustain, defense</t>
   </si>
   <si>
-    <t>寒霜冰箭</t>
-  </si>
-  <si>
     <t>pierce</t>
   </si>
   <si>
@@ -277,9 +268,6 @@
   </si>
   <si>
     <t>pierce, slow, freeze, control</t>
-  </si>
-  <si>
-    <t>新星綻放</t>
   </si>
   <si>
     <t>explosive</t>
@@ -600,6 +588,22 @@
   </si>
   <si>
     <t>nova_bloom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>奧術飛矢</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>聖環飛刃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒霜冰箭</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新星綻放</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2089,43 +2093,43 @@
         <v>48</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="N5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="O5" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="P5" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2134,46 +2138,46 @@
         <v>47</v>
       </c>
       <c r="C6" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>185</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>61</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="I6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="J6" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="L6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="M6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="N6" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2182,46 +2186,46 @@
         <v>47</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>71</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="J7" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="M7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="N7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2230,435 +2234,435 @@
         <v>47</v>
       </c>
       <c r="C8" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>187</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>81</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="K8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="N8" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="N9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="P9" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P9" s="14" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="K10" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="L10" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="M10" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="N10" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="O10" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P10" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="M11" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="N11" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="P11" s="14" t="s">
         <v>123</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="N11" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O11" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="P11" s="14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="K12" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="L12" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="M12" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="N12" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="P12" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="N12" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O12" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="K13" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="L13" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="M13" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="N13" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O13" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="K14" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="L14" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="M14" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="N14" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="O14" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="P14" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="N14" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="O14" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="J15" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="K15" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="L15" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="M15" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="N15" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="O15" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="P15" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="N15" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O15" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="P15" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="K16" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="L16" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="N16" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="O16" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="N16" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O16" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>

--- a/active_skills_spec_12.xlsx
+++ b/active_skills_spec_12.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/active_skills_spec_12.xlsx
+++ b/active_skills_spec_12.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\FirstGameApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mick\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1941C8FC-73C0-493D-A027-621ABDEA4E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B3CFFD-198E-4F4A-862B-A36D4D7A5BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" r:id="rId1"/>
     <sheet name="主動技能規格" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,16 +26,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="190">
   <si>
     <t>主動技能 12 項擴充規格總覽</t>
   </si>
@@ -183,6 +185,9 @@
     <t>arc_bolt</t>
   </si>
   <si>
+    <t>奧術飛矢</t>
+  </si>
+  <si>
     <t>auto</t>
   </si>
   <si>
@@ -216,6 +221,12 @@
     <t>single_target, homing, arcane, starter</t>
   </si>
   <si>
+    <t>halo_disc</t>
+  </si>
+  <si>
+    <t>聖環飛刃</t>
+  </si>
+  <si>
     <t>orbit</t>
   </si>
   <si>
@@ -243,6 +254,12 @@
     <t>orbit, melee, sustain, defense</t>
   </si>
   <si>
+    <t>comet_lance</t>
+  </si>
+  <si>
+    <t>寒霜冰箭</t>
+  </si>
+  <si>
     <t>pierce</t>
   </si>
   <si>
@@ -270,6 +287,12 @@
     <t>pierce, slow, freeze, control</t>
   </si>
   <si>
+    <t>nova_bloom</t>
+  </si>
+  <si>
+    <t>新星綻放</t>
+  </si>
+  <si>
     <t>explosive</t>
   </si>
   <si>
@@ -579,31 +602,11 @@
     <t>建議開發順序：先做 P1（火球、雷擊、砲台、護幕），再做 P2（風刃、地刺、幼龍、圖騰）。</t>
   </si>
   <si>
-    <t>halo_disc</t>
+    <t xml:space="preserve">留意中文編碼問題，不要有亂碼及破壞原本以完善的程式碼，icon、projectile、音效皆已放置至目錄，請一併套用 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>comet_lance</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nova_bloom</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>奧術飛矢</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>聖環飛刃</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒霜冰箭</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>新星綻放</t>
+    <t>node scripts\export-skills-excel.js</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -950,7 +953,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5FF8-416D-BEB7-F9915A36D69B}"/>
+              <c16:uniqueId val="{00000000-96E6-4FBE-9DD4-878288682B47}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2093,43 +2096,43 @@
         <v>48</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2138,46 +2141,46 @@
         <v>47</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2186,46 +2189,46 @@
         <v>47</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2234,435 +2237,435 @@
         <v>47</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I10" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="O10" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>98</v>
-      </c>
       <c r="P10" s="10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11" s="21" t="s">
-        <v>110</v>
-      </c>
       <c r="O11" s="22" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="O12" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="N12" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="O12" s="22" t="s">
-        <v>122</v>
-      </c>
       <c r="P12" s="10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="N13" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N15" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="N16" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -2688,4 +2691,26 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356A6621-3740-4EC4-9EE8-20F549D015D9}">
+  <dimension ref="D15:D17"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/active_skills_spec_12.xlsx
+++ b/active_skills_spec_12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mick\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\FirstGameApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B3CFFD-198E-4F4A-862B-A36D4D7A5BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F983EA19-1091-4DA7-A030-8651DA592B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" r:id="rId1"/>
@@ -545,9 +545,6 @@
     <t>定點緩速、節奏控場</t>
   </si>
   <si>
-    <t>在場上豎立冰晶圖騰，週期性脈衝減速敵人，並可額外發射冰晶碎片。</t>
-  </si>
-  <si>
     <t>圖騰脈衝造成緩速。</t>
   </si>
   <si>
@@ -607,6 +604,10 @@
   </si>
   <si>
     <t>node scripts\export-skills-excel.js</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>在場上豎立冰晶圖騰，週期性脈衝減速敵人，並可額外發射冰晶碎片。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2588,22 +2589,22 @@
         <v>168</v>
       </c>
       <c r="H15" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="K15" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="L15" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="M15" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>174</v>
       </c>
       <c r="N15" s="21" t="s">
         <v>117</v>
@@ -2612,7 +2613,7 @@
         <v>129</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2621,37 +2622,37 @@
         <v>94</v>
       </c>
       <c r="C16" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>176</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>177</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="I16" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="J16" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="K16" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="L16" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="N16" s="21" t="s">
         <v>117</v>
@@ -2660,12 +2661,12 @@
         <v>105</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -2689,7 +2690,8 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2700,12 +2702,12 @@
   <sheetData>
     <row r="15" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
